--- a/Plantilla_SSF_Proyectos_2026.xlsx
+++ b/Plantilla_SSF_Proyectos_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://comfenalcocartagena.sharepoint.com/sites/ProyectoseInnovacin/Proyectos e Innovacin/1. GESTIÓN/2026/Nueva Versión/DB SSF/Visor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{978BEFB8-EF59-42B0-9D0C-0B8D4C4B30F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{242ABF44-386A-4813-BA55-CF47FBB3AC28}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{978BEFB8-EF59-42B0-9D0C-0B8D4C4B30F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF778202-5F14-4E83-825A-CA81B5479E6E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,9 +649,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="170" formatCode="0.000000"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -690,7 +692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -703,6 +705,8 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1136,28 +1140,31 @@
         <v>83361352846</v>
       </c>
       <c r="E2">
-        <v>55434224931</v>
+        <v>59159995633</v>
       </c>
       <c r="F2">
-        <v>17130302369</v>
+        <v>20856073071</v>
       </c>
       <c r="G2">
         <v>45057430284</v>
       </c>
       <c r="H2">
-        <v>27927127915</v>
+        <f>+D2-E2</f>
+        <v>24201357213</v>
       </c>
       <c r="I2">
-        <v>7498929236</v>
+        <v>11679494928</v>
       </c>
       <c r="J2">
         <v>26624427634</v>
       </c>
-      <c r="K2">
-        <v>38</v>
-      </c>
-      <c r="L2">
-        <v>66.5</v>
+      <c r="K2" s="9">
+        <f>+(F2/G2)*100</f>
+        <v>46.287755292618279</v>
+      </c>
+      <c r="L2" s="9">
+        <f>+(E2/D2)*100</f>
+        <v>70.968132849632283</v>
       </c>
       <c r="M2">
         <v>87</v>
@@ -1170,20 +1177,22 @@
       </c>
       <c r="P2" t="str">
         <f ca="1">+IF(Q2&gt;=1,"Faltan "&amp;Q2&amp;" días","Finalizado hace "&amp;(-1*Q2)&amp;" días")</f>
-        <v>Faltan 289 días</v>
+        <v>Faltan 267 días</v>
       </c>
       <c r="Q2" s="6">
         <f ca="1">+O2-TODAY()</f>
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="R2">
         <v>45057430284</v>
       </c>
       <c r="S2">
-        <v>53355180513</v>
+        <f>+E2</f>
+        <v>59159995633</v>
       </c>
       <c r="T2">
-        <v>30006172333</v>
+        <f>+D2-S2</f>
+        <v>24201357213</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -1209,6 +1218,7 @@
         <v>2550910234</v>
       </c>
       <c r="H3">
+        <f t="shared" ref="H3:H22" si="0">+D3-E3</f>
         <v>1874491965</v>
       </c>
       <c r="I3">
@@ -1217,11 +1227,13 @@
       <c r="J3">
         <v>3228918361</v>
       </c>
-      <c r="K3">
-        <v>26.5</v>
-      </c>
-      <c r="L3">
-        <v>74.3</v>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K22" si="1">+(F3/G3)*100</f>
+        <v>26.516741357038281</v>
+      </c>
+      <c r="L3" s="9">
+        <f t="shared" ref="L3:L22" si="2">+(E3/D3)*100</f>
+        <v>74.304248144731787</v>
       </c>
       <c r="M3">
         <v>100</v>
@@ -1233,20 +1245,22 @@
         <v>29</v>
       </c>
       <c r="P3" t="str">
-        <f t="shared" ref="P3:P22" ca="1" si="0">+IF(Q3&gt;=1,"Faltan "&amp;Q3&amp;" días","Finalizado hace "&amp;(-1*Q3)&amp;" días")</f>
-        <v>Finalizado hace 106 días</v>
+        <f t="shared" ref="P3:P22" ca="1" si="3">+IF(Q3&gt;=1,"Faltan "&amp;Q3&amp;" días","Finalizado hace "&amp;(-1*Q3)&amp;" días")</f>
+        <v>Finalizado hace 128 días</v>
       </c>
       <c r="Q3" s="6">
         <f ca="1">+O3-TODAY()</f>
-        <v>-106</v>
+        <v>-128</v>
       </c>
       <c r="R3">
         <v>2550910234</v>
       </c>
       <c r="S3">
+        <f t="shared" ref="S3:S22" si="4">+E3</f>
         <v>5420456926</v>
       </c>
       <c r="T3">
+        <f t="shared" ref="T3:T22" si="5">+D3-S3</f>
         <v>1874491965</v>
       </c>
     </row>
@@ -1273,6 +1287,7 @@
         <v>4034534474</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I4">
@@ -1281,10 +1296,12 @@
       <c r="J4">
         <v>21965465526</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="9">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M4">
@@ -1297,20 +1314,22 @@
         <v>33</v>
       </c>
       <c r="P4" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 198 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 220 días</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" ref="Q4:Q22" ca="1" si="1">+O4-TODAY()</f>
-        <v>-198</v>
+        <f t="shared" ref="Q4:Q22" ca="1" si="6">+O4-TODAY()</f>
+        <v>-220</v>
       </c>
       <c r="R4">
         <v>4034534474</v>
       </c>
       <c r="S4">
-        <v>4034534474</v>
+        <f t="shared" si="4"/>
+        <v>26000000000</v>
       </c>
       <c r="T4">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1337,6 +1356,7 @@
         <v>610665687</v>
       </c>
       <c r="H5">
+        <f t="shared" si="0"/>
         <v>75714649</v>
       </c>
       <c r="I5">
@@ -1345,11 +1365,13 @@
       <c r="J5">
         <v>3551954225</v>
       </c>
-      <c r="K5">
-        <v>87.6</v>
-      </c>
-      <c r="L5">
-        <v>98.2</v>
+      <c r="K5" s="9">
+        <f t="shared" si="1"/>
+        <v>87.601293045960844</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" si="2"/>
+        <v>98.181081852279391</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -1361,20 +1383,22 @@
         <v>36</v>
       </c>
       <c r="P5" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 76 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 98 días</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-76</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-98</v>
       </c>
       <c r="R5">
         <v>610665687</v>
       </c>
       <c r="S5">
-        <v>534951038</v>
+        <f t="shared" si="4"/>
+        <v>4086905263</v>
       </c>
       <c r="T5">
+        <f t="shared" si="5"/>
         <v>75714649</v>
       </c>
     </row>
@@ -1401,6 +1425,7 @@
         <v>0</v>
       </c>
       <c r="H6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I6">
@@ -1409,10 +1434,12 @@
       <c r="J6">
         <v>5000000000</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
+      <c r="K6" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L6" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M6">
@@ -1425,20 +1452,22 @@
         <v>46507</v>
       </c>
       <c r="P6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Faltan 228 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Faltan 206 días</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>228</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>206</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>5000000000</v>
       </c>
       <c r="T6">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1465,6 +1494,7 @@
         <v>403362253</v>
       </c>
       <c r="H7">
+        <f t="shared" si="0"/>
         <v>25697981</v>
       </c>
       <c r="I7">
@@ -1473,11 +1503,13 @@
       <c r="J7">
         <v>157930004</v>
       </c>
-      <c r="K7">
-        <v>95</v>
-      </c>
-      <c r="L7">
-        <v>95.5</v>
+      <c r="K7" s="9">
+        <f t="shared" si="1"/>
+        <v>94.954272282885128</v>
+      </c>
+      <c r="L7" s="9">
+        <f t="shared" si="2"/>
+        <v>95.464830165185077</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -1489,21 +1521,23 @@
         <v>42</v>
       </c>
       <c r="P7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 45 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 67 días</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-45</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-67</v>
       </c>
       <c r="R7">
         <v>403362253</v>
       </c>
       <c r="S7">
-        <v>96976097</v>
+        <f t="shared" si="4"/>
+        <v>540939696</v>
       </c>
       <c r="T7">
-        <v>311731576</v>
+        <f t="shared" si="5"/>
+        <v>25697981</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -1529,6 +1563,7 @@
         <v>392915201</v>
       </c>
       <c r="H8">
+        <f t="shared" si="0"/>
         <v>49861687</v>
       </c>
       <c r="I8">
@@ -1537,11 +1572,13 @@
       <c r="J8">
         <v>149177393</v>
       </c>
-      <c r="K8">
-        <v>89.2</v>
-      </c>
-      <c r="L8">
-        <v>90.9</v>
+      <c r="K8" s="9">
+        <f t="shared" si="1"/>
+        <v>89.214759089964559</v>
+      </c>
+      <c r="L8" s="9">
+        <f t="shared" si="2"/>
+        <v>90.927268064847567</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -1553,21 +1590,23 @@
         <v>42</v>
       </c>
       <c r="P8" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 45 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 67 días</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-45</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-67</v>
       </c>
       <c r="R8">
         <v>392915201</v>
       </c>
       <c r="S8">
-        <v>282530856</v>
+        <f t="shared" si="4"/>
+        <v>499715743</v>
       </c>
       <c r="T8">
-        <v>117869181</v>
+        <f t="shared" si="5"/>
+        <v>49861687</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -1584,17 +1623,17 @@
         <v>7022284573</v>
       </c>
       <c r="E9">
-        <v>167749753</v>
+        <v>170762453</v>
       </c>
       <c r="F9">
-        <v>167749753</v>
+        <v>170762453</v>
       </c>
       <c r="G9">
         <v>3584868483.3000002</v>
       </c>
       <c r="H9">
-        <f>+D9-G9</f>
-        <v>3437416089.6999998</v>
+        <f t="shared" si="0"/>
+        <v>6851522120</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1602,11 +1641,13 @@
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
-        <v>4.6800000000000001E-2</v>
-      </c>
-      <c r="L9">
-        <v>2.3888199999999998E-2</v>
+      <c r="K9" s="9">
+        <f t="shared" si="1"/>
+        <v>4.7634230877783006</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" si="2"/>
+        <v>2.4317222012984918</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -1618,21 +1659,23 @@
         <v>47124</v>
       </c>
       <c r="P9" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Faltan 845 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Faltan 823 días</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>845</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>823</v>
       </c>
       <c r="R9">
         <v>3584868483.3000002</v>
       </c>
       <c r="S9">
-        <v>167749753</v>
+        <f t="shared" si="4"/>
+        <v>170762453</v>
       </c>
       <c r="T9">
-        <v>6854534820</v>
+        <f t="shared" si="5"/>
+        <v>6851522120</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -1649,7 +1692,7 @@
         <v>313920380</v>
       </c>
       <c r="E10">
-        <v>207945667</v>
+        <v>286779096</v>
       </c>
       <c r="F10">
         <v>207451432</v>
@@ -1658,7 +1701,8 @@
         <v>313426145</v>
       </c>
       <c r="H10">
-        <v>105974713</v>
+        <f t="shared" si="0"/>
+        <v>27141284</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1666,11 +1710,13 @@
       <c r="J10">
         <v>494235</v>
       </c>
-      <c r="K10">
-        <v>66.2</v>
-      </c>
-      <c r="L10">
-        <v>66.2</v>
+      <c r="K10" s="9">
+        <f t="shared" si="1"/>
+        <v>66.188298362920548</v>
+      </c>
+      <c r="L10" s="9">
+        <f t="shared" si="2"/>
+        <v>91.35408666363108</v>
       </c>
       <c r="M10">
         <v>94</v>
@@ -1682,21 +1728,23 @@
         <v>49</v>
       </c>
       <c r="P10" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Faltan 77 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Faltan 55 días</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>55</v>
       </c>
       <c r="R10">
         <v>313426145</v>
       </c>
       <c r="S10">
-        <v>96077019</v>
+        <f t="shared" si="4"/>
+        <v>286779096</v>
       </c>
       <c r="T10">
-        <v>217349126</v>
+        <f t="shared" si="5"/>
+        <v>27141284</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -1722,6 +1770,7 @@
         <v>0</v>
       </c>
       <c r="H11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11">
@@ -1730,11 +1779,13 @@
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="K11" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L11" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -1746,20 +1797,22 @@
         <v>52</v>
       </c>
       <c r="P11" t="e">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q11" s="6" t="e">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="R11">
         <v>0</v>
       </c>
       <c r="S11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T11">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1786,6 +1839,7 @@
         <v>0</v>
       </c>
       <c r="H12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I12">
@@ -1794,11 +1848,13 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="K12" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L12" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1810,20 +1866,22 @@
         <v>52</v>
       </c>
       <c r="P12" t="e">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q12" s="6" t="e">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
       <c r="S12">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T12">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1850,6 +1908,7 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I13">
@@ -1858,11 +1917,13 @@
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
+      <c r="K13" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L13" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1874,20 +1935,22 @@
         <v>52</v>
       </c>
       <c r="P13" t="e">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q13" s="6" t="e">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="R13">
         <v>0</v>
       </c>
       <c r="S13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T13">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1905,17 +1968,17 @@
         <v>7233565156</v>
       </c>
       <c r="E14">
-        <v>299406346</v>
+        <v>322069896</v>
       </c>
       <c r="F14">
-        <v>299406346</v>
+        <v>322069896</v>
       </c>
       <c r="G14">
         <v>3477679682</v>
       </c>
       <c r="H14">
-        <f>+D14-G14</f>
-        <v>3755885474</v>
+        <f t="shared" si="0"/>
+        <v>6911495260</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1923,11 +1986,13 @@
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14">
-        <v>8.6099999999999996E-2</v>
-      </c>
-      <c r="L14">
-        <v>4.1391255838990053E-2</v>
+      <c r="K14" s="9">
+        <f t="shared" si="1"/>
+        <v>9.2610569532033171</v>
+      </c>
+      <c r="L14" s="9">
+        <f t="shared" si="2"/>
+        <v>4.4524365102712018</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1939,21 +2004,23 @@
         <v>47075</v>
       </c>
       <c r="P14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Faltan 796 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Faltan 774 días</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>796</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>774</v>
       </c>
       <c r="R14">
         <v>3477679682</v>
       </c>
       <c r="S14">
-        <v>299406346</v>
+        <f t="shared" si="4"/>
+        <v>322069896</v>
       </c>
       <c r="T14">
-        <v>6934158810</v>
+        <f t="shared" si="5"/>
+        <v>6911495260</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -1979,6 +2046,7 @@
         <v>0</v>
       </c>
       <c r="H15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I15">
@@ -1987,11 +2055,13 @@
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
+      <c r="K15" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L15" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -2003,20 +2073,22 @@
         <v>52</v>
       </c>
       <c r="P15" t="e">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q15" s="6" t="e">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="R15">
         <v>0</v>
       </c>
       <c r="S15">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T15">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2043,6 +2115,7 @@
         <v>0</v>
       </c>
       <c r="H16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16">
@@ -2051,11 +2124,13 @@
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
+      <c r="K16" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L16" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -2067,20 +2142,22 @@
         <v>52</v>
       </c>
       <c r="P16" t="e">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q16" s="6" t="e">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
       <c r="S16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2107,8 +2184,8 @@
         <v>1105633771.0693662</v>
       </c>
       <c r="H17">
-        <f>+D17-G17</f>
-        <v>1075633770.9306338</v>
+        <f t="shared" si="0"/>
+        <v>2181267542</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2116,10 +2193,12 @@
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
+      <c r="K17" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M17">
@@ -2132,20 +2211,22 @@
         <v>46623</v>
       </c>
       <c r="P17" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Faltan 344 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Faltan 322 días</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>322</v>
       </c>
       <c r="R17">
         <v>2181267542</v>
       </c>
       <c r="S17">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T17">
+        <f t="shared" si="5"/>
         <v>2181267542</v>
       </c>
     </row>
@@ -2163,16 +2244,17 @@
         <v>28000000000</v>
       </c>
       <c r="E18">
-        <v>17534550222</v>
+        <v>22201161299</v>
       </c>
       <c r="F18">
-        <v>17534550222</v>
+        <v>22201161299</v>
       </c>
       <c r="G18">
         <v>25058924514</v>
       </c>
       <c r="H18">
-        <v>10465449778</v>
+        <f t="shared" si="0"/>
+        <v>5798838701</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2180,11 +2262,13 @@
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
-        <v>70</v>
-      </c>
-      <c r="L18">
-        <v>62.6</v>
+      <c r="K18" s="9">
+        <f t="shared" si="1"/>
+        <v>88.595826555112467</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="2"/>
+        <v>79.28986178214285</v>
       </c>
       <c r="M18">
         <v>62.6</v>
@@ -2196,21 +2280,23 @@
         <v>62</v>
       </c>
       <c r="P18" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Faltan 167 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Faltan 145 días</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>167</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>145</v>
       </c>
       <c r="R18">
         <v>25058924514</v>
       </c>
       <c r="S18">
-        <v>3264353661</v>
+        <f t="shared" si="4"/>
+        <v>22201161299</v>
       </c>
       <c r="T18">
-        <v>24735646339</v>
+        <f t="shared" si="5"/>
+        <v>5798838701</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -2236,6 +2322,7 @@
         <v>0</v>
       </c>
       <c r="H19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I19">
@@ -2244,10 +2331,12 @@
       <c r="J19">
         <v>220396208</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
+      <c r="K19" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M19">
@@ -2260,20 +2349,22 @@
         <v>65</v>
       </c>
       <c r="P19" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 46279 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 46301 días</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-46279</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-46301</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>426800378</v>
       </c>
       <c r="T19">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2300,6 +2391,7 @@
         <v>0</v>
       </c>
       <c r="H20">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I20">
@@ -2308,10 +2400,12 @@
       <c r="J20">
         <v>778000000</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
+      <c r="K20" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M20">
@@ -2324,20 +2418,22 @@
         <v>69</v>
       </c>
       <c r="P20" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 288 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 310 días</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-288</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-310</v>
       </c>
       <c r="R20">
         <v>0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>778000000</v>
       </c>
       <c r="T20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2364,6 +2460,7 @@
         <v>0</v>
       </c>
       <c r="H21">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I21">
@@ -2372,10 +2469,12 @@
       <c r="J21">
         <v>4829814563</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
+      <c r="K21" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M21">
@@ -2388,20 +2487,22 @@
         <v>73</v>
       </c>
       <c r="P21" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 563 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 585 días</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-563</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-585</v>
       </c>
       <c r="R21">
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>26000000000</v>
       </c>
       <c r="T21">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2428,6 +2529,7 @@
         <v>0</v>
       </c>
       <c r="H22">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22">
@@ -2436,10 +2538,12 @@
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
+      <c r="K22" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M22">
@@ -2452,22 +2556,27 @@
         <v>76</v>
       </c>
       <c r="P22" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Finalizado hace 380 días</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>Finalizado hace 402 días</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>-380</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>-402</v>
       </c>
       <c r="R22">
         <v>0</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3000000000</v>
       </c>
       <c r="T22">
-        <v>0</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="G26" s="7"/>
@@ -2492,7 +2601,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:T1 A11:O13 A19:O22 E17:F17 A15:O16 I14:J14 A7:O8 A5:D5 G5 I5:J5 M5:O5 A4:O4 A2:D2 A3:O3 G2 I2:J2 R2 R10:T13 R18:T22 S17 R15:T16 R6:T8 R5 R4:T4 R3 B18:D18 G18 I18:J18 N18:O18 A10:L10 O10 A6:M6 I9:J9 I17:M17 M14 M9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:T1 A11:G13 A19:G22 E17:F17 A15:G16 I14:J14 A7:G8 A5:D5 G5 I5:J5 M5:O5 A4:G4 A2:D2 A3:G3 G2 J2 R2 R10:R13 R18:R22 R15:R16 R6:R8 R5 R4 R3 B18:D18 G18 I18:J18 N18:O18 A10:D10 O10 A6:G6 I9:J9 I17:J17 M14 M9 M11:O13 M19:O22 M15:O16 M7:O8 M4:O4 M3:O3 M6 M17 I11:J13 I19:J22 I15:J16 I7:J8 I4:J4 I3:J3 I10:J10 I6:J6 F10:G10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3973,26 +4082,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f3bd45c0-8d65-4cae-8821-0b25f52f9199" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1b2e05c7-f74e-489c-9b0e-4a2ceb37ccd9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FE78E784CE63B443834FBFF8A36EF5B9" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="78a1ee2dd28d73fe7e4be10b368ab933">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1b2e05c7-f74e-489c-9b0e-4a2ceb37ccd9" xmlns:ns3="f3bd45c0-8d65-4cae-8821-0b25f52f9199" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f99440221b6cce3f2ade21f83c16897b" ns2:_="" ns3:_="">
     <xsd:import namespace="1b2e05c7-f74e-489c-9b0e-4a2ceb37ccd9"/>
@@ -4227,10 +4316,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f3bd45c0-8d65-4cae-8821-0b25f52f9199" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1b2e05c7-f74e-489c-9b0e-4a2ceb37ccd9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED8D8F6-2E4F-427D-8BDE-8DB214A0277A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15567F2F-E200-4E16-BD18-C345B2D8881B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1b2e05c7-f74e-489c-9b0e-4a2ceb37ccd9"/>
+    <ds:schemaRef ds:uri="f3bd45c0-8d65-4cae-8821-0b25f52f9199"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4247,20 +4367,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15567F2F-E200-4E16-BD18-C345B2D8881B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED8D8F6-2E4F-427D-8BDE-8DB214A0277A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1b2e05c7-f74e-489c-9b0e-4a2ceb37ccd9"/>
-    <ds:schemaRef ds:uri="f3bd45c0-8d65-4cae-8821-0b25f52f9199"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>